--- a/results/03-2025/beta/contributions-03-2025.xlsx
+++ b/results/03-2025/beta/contributions-03-2025.xlsx
@@ -22069,88 +22069,88 @@
         <v>-1</v>
       </c>
       <c r="D221" t="n">
-        <v>0.107150873316688</v>
+        <v>0.110561279115709</v>
       </c>
       <c r="E221" t="n">
-        <v>-0.011366028688026</v>
+        <v>0.0203237932082108</v>
       </c>
       <c r="F221" t="n">
-        <v>0.352570134160248</v>
+        <v>0.352356703711459</v>
       </c>
       <c r="G221" t="n">
-        <v>-0.00616450493471536</v>
+        <v>-0.0138441171093988</v>
       </c>
       <c r="H221" t="n">
-        <v>-0.043263388877005</v>
+        <v>-0.0446147184625543</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.134158072261678</v>
+        <v>-0.133978344448316</v>
       </c>
       <c r="J221" t="n">
-        <v>0.0132320470285215</v>
+        <v>0.0127711857040583</v>
       </c>
       <c r="K221" t="n">
-        <v>0.173003157723465</v>
+        <v>0.168881316037664</v>
       </c>
       <c r="L221" t="n">
-        <v>0.00964915074866303</v>
+        <v>0.00972683995754284</v>
       </c>
       <c r="M221" t="n">
         <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>-0.100852977945604</v>
+        <v>-0.100735987081741</v>
       </c>
       <c r="O221" t="n">
-        <v>-0.000173512536473991</v>
+        <v>-0.000173322100297906</v>
       </c>
       <c r="P221" t="n">
-        <v>0.00364483446927851</v>
+        <v>0.00365536653191232</v>
       </c>
       <c r="Q221" t="n">
-        <v>-0.151329872047867</v>
+        <v>-0.151133932937553</v>
       </c>
       <c r="R221" t="n">
-        <v>-0.0291775594193379</v>
+        <v>-0.0291425366831609</v>
       </c>
       <c r="S221" t="n">
-        <v>-0.0223872422655659</v>
+        <v>-0.0223595035571501</v>
       </c>
       <c r="T221" t="n">
-        <v>-0.0266478280873095</v>
+        <v>-0.0266165012063223</v>
       </c>
       <c r="U221" t="n">
-        <v>-0.0308134352314298</v>
+        <v>-0.0307768237558101</v>
       </c>
       <c r="V221" t="n">
-        <v>-0.0000541637421126199</v>
+        <v>-0.0000539207800531854</v>
       </c>
       <c r="W221" t="n">
-        <v>0.152861670376723</v>
+        <v>0.153397683237875</v>
       </c>
       <c r="X221" t="n">
-        <v>0.145236653229646</v>
+        <v>0.104132746222464</v>
       </c>
       <c r="Y221" t="n">
-        <v>0.0741955630503683</v>
+        <v>0.0789199903093441</v>
       </c>
       <c r="Z221" t="n">
-        <v>0.0215892815782934</v>
+        <v>0.0519650820145759</v>
       </c>
       <c r="AA221" t="n">
-        <v>0.182792492079279</v>
+        <v>0.173285721695267</v>
       </c>
       <c r="AB221" t="n">
-        <v>0.123452917116291</v>
+        <v>0.0792824983544705</v>
       </c>
       <c r="AC221" t="n">
-        <v>0.306011520747354</v>
+        <v>0.25242563744184</v>
       </c>
       <c r="AD221" t="n">
-        <v>0.401796365376016</v>
+        <v>0.38331070976576</v>
       </c>
       <c r="AE221" t="n">
-        <v>0.254532467800564</v>
+        <v>0.249911053898</v>
       </c>
     </row>
     <row r="222">
@@ -22164,88 +22164,88 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.34812269649394</v>
+        <v>-0.34807233541767</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.161446108278581</v>
+        <v>-0.161509230103792</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0107685291377733</v>
+        <v>0.128623060016345</v>
       </c>
       <c r="G222" t="n">
-        <v>-0.00362511891593439</v>
+        <v>0.0367486177984778</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.0386102743233363</v>
+        <v>-0.033858231617597</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0272327215780774</v>
+        <v>0.0248108666850174</v>
       </c>
       <c r="J222" t="n">
-        <v>0.0140214378438707</v>
+        <v>0.0181929384174016</v>
       </c>
       <c r="K222" t="n">
-        <v>0.0104374406536559</v>
+        <v>-0.0597531630263302</v>
       </c>
       <c r="L222" t="n">
-        <v>0.0286274791953285</v>
+        <v>0.0220486805515956</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>-0.0969948095236936</v>
+        <v>-0.0974514069022635</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.000872664091383299</v>
+        <v>-0.00195508224475647</v>
       </c>
       <c r="Q222" t="n">
-        <v>-0.0787045902525759</v>
+        <v>-0.0809178479718922</v>
       </c>
       <c r="R222" t="n">
-        <v>-0.0280715359290164</v>
+        <v>-0.0282909934311354</v>
       </c>
       <c r="S222" t="n">
-        <v>-0.0148326651704783</v>
+        <v>-0.0150665346836312</v>
       </c>
       <c r="T222" t="n">
-        <v>-0.010526635232305</v>
+        <v>-0.0106801048666019</v>
       </c>
       <c r="U222" t="n">
-        <v>-0.03008222459157</v>
+        <v>-0.0302860085046919</v>
       </c>
       <c r="V222" t="n">
-        <v>-0.000772880260457906</v>
+        <v>-0.000786438207269989</v>
       </c>
       <c r="W222" t="n">
-        <v>0.247727825279121</v>
+        <v>0.192071065267204</v>
       </c>
       <c r="X222" t="n">
-        <v>0.0449923871213833</v>
+        <v>0.0245907857035634</v>
       </c>
       <c r="Y222" t="n">
-        <v>-0.671715703854223</v>
+        <v>-0.671616183795975</v>
       </c>
       <c r="Z222" t="n">
-        <v>0.162146899081702</v>
+        <v>0.162034618274513</v>
       </c>
       <c r="AA222" t="n">
-        <v>0.00980026746305165</v>
+        <v>0.17446202281295</v>
       </c>
       <c r="AB222" t="n">
-        <v>0.0713327295060325</v>
+        <v>-0.0862014272221448</v>
       </c>
       <c r="AC222" t="n">
-        <v>0.0811256283481254</v>
+        <v>0.0884191935588332</v>
       </c>
       <c r="AD222" t="n">
-        <v>-0.428443176424396</v>
+        <v>-0.421162371962629</v>
       </c>
       <c r="AE222" t="n">
-        <v>0.148720358563503</v>
+        <v>0.145919145776381</v>
       </c>
     </row>
     <row r="223">
@@ -22259,88 +22259,88 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.247897737351378</v>
+        <v>-0.24786187529187</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.198269595892895</v>
+        <v>-0.198347114879943</v>
       </c>
       <c r="F223" t="n">
-        <v>0.0191635970233239</v>
+        <v>0.0738429727958706</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.0197427348749497</v>
+        <v>-0.0102909133218752</v>
       </c>
       <c r="H223" t="n">
-        <v>-0.029584098165249</v>
+        <v>-0.0290469148572916</v>
       </c>
       <c r="I223" t="n">
-        <v>0.18707964577705</v>
+        <v>0.186302366043517</v>
       </c>
       <c r="J223" t="n">
-        <v>0.00735737740620022</v>
+        <v>0.00992866969397865</v>
       </c>
       <c r="K223" t="n">
-        <v>-0.0330876535616735</v>
+        <v>-0.0574918282431275</v>
       </c>
       <c r="L223" t="n">
-        <v>0.0286394445162739</v>
+        <v>0.0266253294861937</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>-0.0950805508069859</v>
+        <v>-0.0951382512989328</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.00216932574867619</v>
+        <v>-0.00249588957091823</v>
       </c>
       <c r="Q223" t="n">
-        <v>-0.11449131433406</v>
+        <v>-0.115090482244711</v>
       </c>
       <c r="R223" t="n">
-        <v>-0.0267845543866995</v>
+        <v>-0.0268277799669606</v>
       </c>
       <c r="S223" t="n">
-        <v>-0.0135215529242429</v>
+        <v>-0.0135801567312405</v>
       </c>
       <c r="T223" t="n">
-        <v>-0.0100469027546833</v>
+        <v>-0.0100846452948945</v>
       </c>
       <c r="U223" t="n">
-        <v>-0.0237798353383869</v>
+        <v>-0.0238173690691484</v>
       </c>
       <c r="V223" t="n">
-        <v>-0.0014480049834142</v>
+        <v>-0.00145136621054944</v>
       </c>
       <c r="W223" t="n">
-        <v>0.255069401121969</v>
+        <v>0.235785543905884</v>
       </c>
       <c r="X223" t="n">
-        <v>0.0330444313257097</v>
+        <v>0.0161436959622865</v>
       </c>
       <c r="Y223" t="n">
-        <v>-0.451072062860655</v>
+        <v>-0.451006033934209</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.00490472961638176</v>
+        <v>0.00479704376239564</v>
       </c>
       <c r="AA223" t="n">
-        <v>0.164324700557513</v>
+        <v>0.230672924787921</v>
       </c>
       <c r="AB223" t="n">
-        <v>-0.00317405570746418</v>
+        <v>-0.0670064974900477</v>
       </c>
       <c r="AC223" t="n">
-        <v>0.161156121911072</v>
+        <v>0.163828818702443</v>
       </c>
       <c r="AD223" t="n">
-        <v>-0.285011211333202</v>
+        <v>-0.28238017146937</v>
       </c>
       <c r="AE223" t="n">
-        <v>0.0474435069173137</v>
+        <v>0.0453000540961496</v>
       </c>
     </row>
     <row r="224">
@@ -22354,88 +22354,88 @@
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.165623756991551</v>
+        <v>-0.165599797075286</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.186884898300513</v>
+        <v>-0.186957966124883</v>
       </c>
       <c r="F224" t="n">
-        <v>0.0635512501973908</v>
+        <v>0.0951282482175262</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.0180879943783451</v>
+        <v>-0.0125609869783847</v>
       </c>
       <c r="H224" t="n">
-        <v>-0.0436583349794452</v>
+        <v>-0.0437378234889283</v>
       </c>
       <c r="I224" t="n">
-        <v>0.18586463155258</v>
+        <v>0.185248920687634</v>
       </c>
       <c r="J224" t="n">
-        <v>0.00777369979516931</v>
+        <v>0.0100693914834305</v>
       </c>
       <c r="K224" t="n">
-        <v>-0.0629538330084869</v>
+        <v>-0.0805610689963742</v>
       </c>
       <c r="L224" t="n">
-        <v>0.00951346206366038</v>
+        <v>0.0081627600234598</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>-0.000996294750735312</v>
+        <v>-0.000997572128635847</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.00392923037084015</v>
+        <v>-0.00414475766779126</v>
       </c>
       <c r="Q224" t="n">
-        <v>-0.0900478608909075</v>
+        <v>-0.0903883313122512</v>
       </c>
       <c r="R224" t="n">
-        <v>-0.0260749383790248</v>
+        <v>-0.0260894918240007</v>
       </c>
       <c r="S224" t="n">
-        <v>-0.013701462629103</v>
+        <v>-0.0137331664428794</v>
       </c>
       <c r="T224" t="n">
-        <v>-0.00847322450313509</v>
+        <v>-0.00849317388269535</v>
       </c>
       <c r="U224" t="n">
-        <v>0.000180292621668077</v>
+        <v>0.00016456130624153</v>
       </c>
       <c r="V224" t="n">
-        <v>-0.000422876186853873</v>
+        <v>-0.000424486270931437</v>
       </c>
       <c r="W224" t="n">
-        <v>0.229874822529572</v>
+        <v>0.21631145496191</v>
       </c>
       <c r="X224" t="n">
-        <v>0.0650628541464284</v>
+        <v>0.0460694386973623</v>
       </c>
       <c r="Y224" t="n">
-        <v>-0.219720493872276</v>
+        <v>-0.219688692601391</v>
       </c>
       <c r="Z224" t="n">
-        <v>-0.132788161419787</v>
+        <v>-0.132869070598779</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.195457333484598</v>
+        <v>0.234098573332597</v>
       </c>
       <c r="AB224" t="n">
-        <v>0.0983516726802031</v>
+        <v>0.0462064836773189</v>
       </c>
       <c r="AC224" t="n">
-        <v>0.29360592812621</v>
+        <v>0.280190732868275</v>
       </c>
       <c r="AD224" t="n">
-        <v>-0.0589027271658538</v>
+        <v>-0.0723670303318942</v>
       </c>
       <c r="AE224" t="n">
-        <v>-0.0926401873868594</v>
+        <v>-0.0981497159995337</v>
       </c>
     </row>
     <row r="225">
@@ -22449,88 +22449,88 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.16345070293878</v>
+        <v>-0.163427057386796</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.185916696647066</v>
+        <v>-0.185989385926198</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0776712627364136</v>
+        <v>0.0911553021237632</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.00951916342499131</v>
+        <v>-0.0138684110203533</v>
       </c>
       <c r="H225" t="n">
-        <v>-0.0386834152565656</v>
+        <v>-0.039976406623415</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0727857675446842</v>
+        <v>0.0727752280488825</v>
       </c>
       <c r="J225" t="n">
-        <v>0.00914651764625598</v>
+        <v>0.0109642602531611</v>
       </c>
       <c r="K225" t="n">
-        <v>-0.152434624461755</v>
+        <v>-0.152233302734978</v>
       </c>
       <c r="L225" t="n">
-        <v>0.031069649235347</v>
+        <v>0.0310651527380555</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>-0.000974558269637336</v>
+        <v>-0.000974417287214013</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.00486879867638218</v>
+        <v>-0.00486809437744442</v>
       </c>
       <c r="Q225" t="n">
-        <v>-0.0513879347388036</v>
+        <v>-0.0513805056792026</v>
       </c>
       <c r="R225" t="n">
-        <v>-0.00390945658319908</v>
+        <v>-0.00390889105140617</v>
       </c>
       <c r="S225" t="n">
-        <v>-0.0128604703583512</v>
+        <v>-0.012858610212686</v>
       </c>
       <c r="T225" t="n">
-        <v>-0.0076769927369462</v>
+        <v>-0.00767588225761748</v>
       </c>
       <c r="U225" t="n">
-        <v>0.000120018142809031</v>
+        <v>0.000120000780400383</v>
       </c>
       <c r="V225" t="n">
-        <v>-0.0003928012630834</v>
+        <v>-0.000392744438882796</v>
       </c>
       <c r="W225" t="n">
-        <v>0.176375078029272</v>
+        <v>0.174732240873678</v>
       </c>
       <c r="X225" t="n">
-        <v>0.0456891245892075</v>
+        <v>0.0636305176693273</v>
       </c>
       <c r="Y225" t="n">
-        <v>-0.269913096075334</v>
+        <v>-0.269873893087066</v>
       </c>
       <c r="Z225" t="n">
-        <v>-0.0794543035105125</v>
+        <v>-0.0795425502259275</v>
       </c>
       <c r="AA225" t="n">
-        <v>0.111404066224449</v>
+        <v>0.121054503565346</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.0190653212280896</v>
+        <v>0.0355749327257865</v>
       </c>
       <c r="AC225" t="n">
-        <v>0.130446916034948</v>
+        <v>0.156583848598439</v>
       </c>
       <c r="AD225" t="n">
-        <v>-0.218920483550899</v>
+        <v>-0.192832594714555</v>
       </c>
       <c r="AE225" t="n">
-        <v>-0.247819399618588</v>
+        <v>-0.242185542119612</v>
       </c>
     </row>
     <row r="226">
@@ -22544,88 +22544,88 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.145631825556942</v>
+        <v>-0.145610757768061</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.184744395363472</v>
+        <v>-0.184816626298966</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.00867677039099331</v>
+        <v>0.00554274233333005</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.0148987391943528</v>
+        <v>-0.0192037248724259</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.0242704833921742</v>
+        <v>-0.0255273887007913</v>
       </c>
       <c r="I226" t="n">
-        <v>0.315692954023002</v>
+        <v>0.315647096002186</v>
       </c>
       <c r="J226" t="n">
-        <v>0.00725991836711011</v>
+        <v>0.0090385176108663</v>
       </c>
       <c r="K226" t="n">
-        <v>-0.150055021092008</v>
+        <v>-0.149857613903128</v>
       </c>
       <c r="L226" t="n">
-        <v>0.010053390320148</v>
+        <v>0.0100519357583922</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>-0.000952000380025069</v>
+        <v>-0.000951862660917075</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.00441793686412618</v>
+        <v>-0.00441729778133097</v>
       </c>
       <c r="Q226" t="n">
-        <v>-0.018510124049966</v>
+        <v>-0.0185074469342457</v>
       </c>
       <c r="R226" t="n">
-        <v>-0.00267817606184217</v>
+        <v>-0.00267778863779279</v>
       </c>
       <c r="S226" t="n">
-        <v>-0.0143507467896208</v>
+        <v>-0.0143486711313129</v>
       </c>
       <c r="T226" t="n">
-        <v>-0.00706784131765174</v>
+        <v>-0.00706681894458921</v>
       </c>
       <c r="U226" t="n">
-        <v>-0.000164333077580123</v>
+        <v>-0.000164309304481238</v>
       </c>
       <c r="V226" t="n">
-        <v>-0.000341829275316612</v>
+        <v>-0.000341779824937482</v>
       </c>
       <c r="W226" t="n">
-        <v>0.0944351457288708</v>
+        <v>0.0904282203585646</v>
       </c>
       <c r="X226" t="n">
-        <v>0.0235824536144519</v>
+        <v>0.0170032032403414</v>
       </c>
       <c r="Y226" t="n">
-        <v>-0.19925767927302</v>
+        <v>-0.199228837929363</v>
       </c>
       <c r="Z226" t="n">
-        <v>-0.131118541647394</v>
+        <v>-0.131198546137664</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.275239234378854</v>
+        <v>0.28559957013599</v>
       </c>
       <c r="AB226" t="n">
-        <v>-0.0703196787891154</v>
+        <v>-0.0807168206429782</v>
       </c>
       <c r="AC226" t="n">
-        <v>0.205125122840537</v>
+        <v>0.205127715358555</v>
       </c>
       <c r="AD226" t="n">
-        <v>-0.125251098079876</v>
+        <v>-0.125299668708472</v>
       </c>
       <c r="AE226" t="n">
-        <v>-0.172021380032458</v>
+        <v>-0.168219866306073</v>
       </c>
     </row>
     <row r="227">
@@ -22639,31 +22639,31 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.147367112149997</v>
+        <v>-0.147345793326348</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.195714168583914</v>
+        <v>-0.195790688455915</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.0332189410306446</v>
+        <v>-0.0191591605073517</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.00332478686040428</v>
+        <v>-0.00760068941240656</v>
       </c>
       <c r="H227" t="n">
-        <v>-0.0249874737051534</v>
+        <v>-0.0262140708583148</v>
       </c>
       <c r="I227" t="n">
-        <v>0.250424968075351</v>
+        <v>0.25038862205937</v>
       </c>
       <c r="J227" t="n">
-        <v>0.00843355229919704</v>
+        <v>0.0101840448666672</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.144165636180601</v>
+        <v>-0.143975916833777</v>
       </c>
       <c r="L227" t="n">
-        <v>0.0110086577109504</v>
+        <v>0.0110070649180479</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -22675,52 +22675,52 @@
         <v>0</v>
       </c>
       <c r="P227" t="n">
-        <v>-0.00414552816847914</v>
+        <v>-0.00414492848911679</v>
       </c>
       <c r="Q227" t="n">
-        <v>-0.0142818564061106</v>
+        <v>-0.0142797907095622</v>
       </c>
       <c r="R227" t="n">
-        <v>-0.0022490972874036</v>
+        <v>-0.00224877193185339</v>
       </c>
       <c r="S227" t="n">
-        <v>-0.0098742171520722</v>
+        <v>-0.00987278888483186</v>
       </c>
       <c r="T227" t="n">
-        <v>-0.00649054439537933</v>
+        <v>-0.0064896055218749</v>
       </c>
       <c r="U227" t="n">
-        <v>-0.000192770505025867</v>
+        <v>-0.000192742617953307</v>
       </c>
       <c r="V227" t="n">
-        <v>-0.000334987103008061</v>
+        <v>-0.000334938642375072</v>
       </c>
       <c r="W227" t="n">
-        <v>0.0982709301114543</v>
+        <v>0.0933403953773657</v>
       </c>
       <c r="X227" t="n">
-        <v>0.0190887418329028</v>
+        <v>0.0134914933600996</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.233530005341908</v>
+        <v>-0.233496140866861</v>
       </c>
       <c r="Z227" t="n">
-        <v>-0.109551275392002</v>
+        <v>-0.109640340915402</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.197463041084425</v>
+        <v>0.207709209323055</v>
       </c>
       <c r="AB227" t="n">
-        <v>-0.0532154834629245</v>
+        <v>-0.0635623113526104</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.144359020251566</v>
+        <v>0.144287010854088</v>
       </c>
       <c r="AD227" t="n">
-        <v>-0.198722260482345</v>
+        <v>-0.198849470928175</v>
       </c>
       <c r="AE227" t="n">
-        <v>-0.150449142319744</v>
+        <v>-0.147337191170775</v>
       </c>
     </row>
     <row r="228">
@@ -22734,31 +22734,31 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.139691278547532</v>
+        <v>-0.139671070146288</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.185612206298268</v>
+        <v>-0.18568477652847</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0408990275306336</v>
+        <v>0.0542151548300115</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0106520855188045</v>
+        <v>0.0064269601360602</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.0130419479830668</v>
+        <v>-0.0142325694621497</v>
       </c>
       <c r="I228" t="n">
-        <v>0.077405289584621</v>
+        <v>0.0773940804122464</v>
       </c>
       <c r="J228" t="n">
-        <v>0.00986529982926714</v>
+        <v>0.0115717825744907</v>
       </c>
       <c r="K228" t="n">
-        <v>-0.139223319797929</v>
+        <v>-0.13903737460636</v>
       </c>
       <c r="L228" t="n">
-        <v>0.0111904487412982</v>
+        <v>0.0111888296407943</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -22770,52 +22770,52 @@
         <v>0</v>
       </c>
       <c r="P228" t="n">
-        <v>-0.00453736195097931</v>
+        <v>-0.0045367055937085</v>
       </c>
       <c r="Q228" t="n">
-        <v>-0.0131372879719407</v>
+        <v>-0.0131353877966352</v>
       </c>
       <c r="R228" t="n">
-        <v>-0.00283816075296156</v>
+        <v>-0.00283775018638929</v>
       </c>
       <c r="S228" t="n">
-        <v>-0.00673364041288035</v>
+        <v>-0.00673266637844757</v>
       </c>
       <c r="T228" t="n">
-        <v>-0.00578966512410781</v>
+        <v>-0.00578882762720297</v>
       </c>
       <c r="U228" t="n">
-        <v>-0.00729566873282012</v>
+        <v>-0.00729461340764343</v>
       </c>
       <c r="V228" t="n">
-        <v>-0.000327172459639406</v>
+        <v>-0.000327125129496511</v>
       </c>
       <c r="W228" t="n">
-        <v>0.0924703218328053</v>
+        <v>0.0859794638440001</v>
       </c>
       <c r="X228" t="n">
-        <v>0.0168053403300093</v>
+        <v>0.0129305572545991</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.175226623214915</v>
+        <v>-0.175201272972773</v>
       </c>
       <c r="Z228" t="n">
-        <v>-0.150076861630886</v>
+        <v>-0.150154573701984</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.125738296130897</v>
+        <v>0.135327289238752</v>
       </c>
       <c r="AB228" t="n">
-        <v>-0.0592821129504645</v>
+        <v>-0.069471546754662</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.0665356657064532</v>
+        <v>0.0659560398497216</v>
       </c>
       <c r="AD228" t="n">
-        <v>-0.258767819139347</v>
+        <v>-0.259399806825036</v>
       </c>
       <c r="AE228" t="n">
-        <v>-0.200415415313117</v>
+        <v>-0.19409538529406</v>
       </c>
     </row>
     <row r="229">
@@ -22829,31 +22829,31 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.157847394340289</v>
+        <v>-0.157824559389436</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.196305284080939</v>
+        <v>-0.196382035065907</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0626635817444789</v>
+        <v>0.0751936609825237</v>
       </c>
       <c r="G229" t="n">
-        <v>0.0227170465156699</v>
+        <v>0.0216897405606269</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.00555940819187405</v>
+        <v>-0.00672205644484536</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0529491890680316</v>
+        <v>-0.0529415344848124</v>
       </c>
       <c r="J229" t="n">
-        <v>0.0101259760929233</v>
+        <v>0.0118046627460373</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.0893103752649634</v>
+        <v>-0.0891328104198866</v>
       </c>
       <c r="L229" t="n">
-        <v>0.0113245577579837</v>
+        <v>0.0113229192515197</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -22865,52 +22865,52 @@
         <v>0</v>
       </c>
       <c r="P229" t="n">
-        <v>-0.00465626323656946</v>
+        <v>-0.00465558968047802</v>
       </c>
       <c r="Q229" t="n">
-        <v>-0.0112121827482052</v>
+        <v>-0.0112105609784104</v>
       </c>
       <c r="R229" t="n">
-        <v>-0.000298682541668834</v>
+        <v>-0.000298639333036253</v>
       </c>
       <c r="S229" t="n">
-        <v>-0.00307668206262129</v>
+        <v>-0.00307623699312262</v>
       </c>
       <c r="T229" t="n">
-        <v>-0.00321818598360054</v>
+        <v>-0.00321772044516816</v>
       </c>
       <c r="U229" t="n">
-        <v>-0.0061659531098135</v>
+        <v>-0.00616506118569692</v>
       </c>
       <c r="V229" t="n">
-        <v>-0.000321819308917466</v>
+        <v>-0.00032177275317686</v>
       </c>
       <c r="W229" t="n">
-        <v>0.0963273722433284</v>
+        <v>0.0895500774099189</v>
       </c>
       <c r="X229" t="n">
-        <v>0.0154431320489032</v>
+        <v>0.0152543628250496</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.218321730117281</v>
+        <v>-0.218290123147988</v>
       </c>
       <c r="Z229" t="n">
-        <v>-0.135830948303947</v>
+        <v>-0.135916471307354</v>
       </c>
       <c r="AA229" t="n">
-        <v>0.0370299617194311</v>
+        <v>0.0490601536526196</v>
       </c>
       <c r="AB229" t="n">
-        <v>0.00492959763518629</v>
+        <v>-0.00186310404165703</v>
       </c>
       <c r="AC229" t="n">
-        <v>0.0419576177996649</v>
+        <v>0.0471980222958405</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.312195060621563</v>
+        <v>-0.307008572159502</v>
       </c>
       <c r="AE229" t="n">
-        <v>-0.223734059580783</v>
+        <v>-0.222639379655297</v>
       </c>
     </row>
     <row r="230">
@@ -22924,31 +22924,31 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-6.26966728142779</v>
+        <v>-6.26876028169659</v>
       </c>
       <c r="E230" t="n">
-        <v>-10.8442926345</v>
+        <v>-10.848532510899</v>
       </c>
       <c r="F230" t="n">
-        <v>7.30983911401378</v>
+        <v>7.28203377958185</v>
       </c>
       <c r="G230" t="n">
-        <v>4.13093177963875</v>
+        <v>4.13895183546246</v>
       </c>
       <c r="H230" t="n">
-        <v>0.224464357740274</v>
+        <v>0.224551046290955</v>
       </c>
       <c r="I230" t="n">
-        <v>-2.09832107244378</v>
+        <v>-2.09802572697468</v>
       </c>
       <c r="J230" t="n">
-        <v>0.0815338425525267</v>
+        <v>0.0813750026900862</v>
       </c>
       <c r="K230" t="n">
-        <v>-7.04416989103243</v>
+        <v>-7.03835633941625</v>
       </c>
       <c r="L230" t="n">
-        <v>-0.728760980647201</v>
+        <v>-0.728656552568863</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
@@ -22960,52 +22960,52 @@
         <v>0</v>
       </c>
       <c r="P230" t="n">
-        <v>-0.0958222629062048</v>
+        <v>-0.0958084181215171</v>
       </c>
       <c r="Q230" t="n">
-        <v>-0.0656680179440577</v>
+        <v>-0.0656585262323876</v>
       </c>
       <c r="R230" t="n">
-        <v>-0.000293221721984725</v>
+        <v>-0.000293179303325571</v>
       </c>
       <c r="S230" t="n">
-        <v>-0.0013737253862283</v>
+        <v>-0.00137352666018494</v>
       </c>
       <c r="T230" t="n">
-        <v>-0.00181971523414214</v>
+        <v>-0.0018194519917686</v>
       </c>
       <c r="U230" t="n">
-        <v>-0.00571969041232334</v>
+        <v>-0.00571886303652414</v>
       </c>
       <c r="V230" t="n">
-        <v>-0.000255515213330649</v>
+        <v>-0.000255478249368487</v>
       </c>
       <c r="W230" t="n">
-        <v>-6.01889610366008</v>
+        <v>-6.01032777338806</v>
       </c>
       <c r="X230" t="n">
-        <v>-1.0163157276317</v>
+        <v>-0.997046823485907</v>
       </c>
       <c r="Y230" t="n">
-        <v>-7.95445474040605</v>
+        <v>-7.95330401135018</v>
       </c>
       <c r="Z230" t="n">
-        <v>-9.15950517552169</v>
+        <v>-9.16398878124539</v>
       </c>
       <c r="AA230" t="n">
-        <v>9.5422179733159</v>
+        <v>9.52281545964804</v>
       </c>
       <c r="AB230" t="n">
-        <v>-15.6996103105912</v>
+        <v>-15.6619981396013</v>
       </c>
       <c r="AC230" t="n">
-        <v>-4.57786837434647</v>
+        <v>-4.56583842420805</v>
       </c>
       <c r="AD230" t="n">
-        <v>-21.6918282902742</v>
+        <v>-21.6831312168036</v>
       </c>
       <c r="AE230" t="n">
-        <v>-5.61537835762937</v>
+        <v>-5.61209726667909</v>
       </c>
     </row>
     <row r="231">
@@ -23025,25 +23025,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F231" t="n">
-        <v>7.1882316620937</v>
+        <v>7.16089662190369</v>
       </c>
       <c r="G231" t="n">
-        <v>4.07962742075285</v>
+        <v>4.08756767790231</v>
       </c>
       <c r="H231" t="n">
-        <v>0.233493070534625</v>
+        <v>0.233576094642379</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0.076999375157603</v>
+        <v>0.0768440680865475</v>
       </c>
       <c r="K231" t="n">
-        <v>-6.89714563482358</v>
+        <v>-6.89146685651106</v>
       </c>
       <c r="L231" t="n">
-        <v>-0.722212289365687</v>
+        <v>-0.722108795149506</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -23055,31 +23055,31 @@
         <v>0</v>
       </c>
       <c r="P231" t="n">
-        <v>-0.0800890049273614</v>
+        <v>-0.0800774310250033</v>
       </c>
       <c r="Q231" t="n">
-        <v>-0.0551600601107615</v>
+        <v>-0.0551520861607341</v>
       </c>
       <c r="R231" t="n">
-        <v>-0.000286481166607188</v>
+        <v>-0.000286439723018561</v>
       </c>
       <c r="S231" t="n">
-        <v>-0.00103684256620762</v>
+        <v>-0.00103669257368984</v>
       </c>
       <c r="T231" t="n">
-        <v>-0.00153041185551572</v>
+        <v>-0.00153019046333154</v>
       </c>
       <c r="U231" t="n">
-        <v>-0.00526080467610503</v>
+        <v>-0.00526004367572175</v>
       </c>
       <c r="V231" t="n">
-        <v>-0.000249697992269249</v>
+        <v>-0.000249661869872005</v>
       </c>
       <c r="W231" t="n">
-        <v>-5.96544292040139</v>
+        <v>-5.95599254739096</v>
       </c>
       <c r="X231" t="n">
-        <v>-1.00680905377357</v>
+        <v>-0.986159667818817</v>
       </c>
       <c r="Y231" t="e">
         <v>#NUM!</v>
@@ -23088,19 +23088,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA231" t="n">
-        <v>11.2218875944419</v>
+        <v>11.2029201178828</v>
       </c>
       <c r="AB231" t="n">
-        <v>-15.4350124681937</v>
+        <v>-15.3950478614055</v>
       </c>
       <c r="AC231" t="n">
-        <v>-2.37164822706985</v>
+        <v>-2.35757063486698</v>
       </c>
       <c r="AD231" t="n">
         <v>0</v>
       </c>
       <c r="AE231" t="n">
-        <v>-5.56569779250878</v>
+        <v>-5.56238489894704</v>
       </c>
     </row>
     <row r="232">
@@ -23120,25 +23120,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F232" t="n">
-        <v>3.62575606280684</v>
+        <v>3.61176717512144</v>
       </c>
       <c r="G232" t="n">
-        <v>2.04810358325155</v>
+        <v>2.05212567193856</v>
       </c>
       <c r="H232" t="n">
-        <v>0.228944613301555</v>
+        <v>0.229026598581487</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>0.0749526254776213</v>
+        <v>0.0747997158212242</v>
       </c>
       <c r="K232" t="n">
-        <v>-6.78245317791429</v>
+        <v>-6.77688548195684</v>
       </c>
       <c r="L232" t="n">
-        <v>-0.718355438015802</v>
+        <v>-0.718252492263566</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
@@ -23150,31 +23150,31 @@
         <v>0</v>
       </c>
       <c r="P232" t="n">
-        <v>-0.0740680646305141</v>
+        <v>-0.0740573599982524</v>
       </c>
       <c r="Q232" t="n">
-        <v>-0.0514975261317439</v>
+        <v>-0.0514900812861928</v>
       </c>
       <c r="R232" t="n">
-        <v>-0.0002808577611383</v>
+        <v>-0.00028081713108898</v>
       </c>
       <c r="S232" t="n">
-        <v>-0.00102092943827411</v>
+        <v>-0.00102078174780352</v>
       </c>
       <c r="T232" t="n">
-        <v>-0.00126503214492442</v>
+        <v>-0.00126484914246346</v>
       </c>
       <c r="U232" t="n">
-        <v>-0.00313174453349087</v>
+        <v>-0.0031312914991257</v>
       </c>
       <c r="V232" t="n">
-        <v>-0.000244879024604515</v>
+        <v>-0.000244843599377984</v>
       </c>
       <c r="W232" t="n">
-        <v>-5.93436378271134</v>
+        <v>-5.92373570951934</v>
       </c>
       <c r="X232" t="n">
-        <v>-1.00097329776254</v>
+        <v>-0.979125386036075</v>
       </c>
       <c r="Y232" t="e">
         <v>#NUM!</v>
@@ -23183,19 +23183,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA232" t="n">
-        <v>5.87913812367661</v>
+        <v>5.86924168442917</v>
       </c>
       <c r="AB232" t="n">
-        <v>-15.2525791973898</v>
+        <v>-15.210120799632</v>
       </c>
       <c r="AC232" t="n">
-        <v>-8.42927053661975</v>
+        <v>-8.40041500333856</v>
       </c>
       <c r="AD232" t="n">
         <v>0</v>
       </c>
       <c r="AE232" t="n">
-        <v>-5.50100583772395</v>
+        <v>-5.49753494724078</v>
       </c>
     </row>
     <row r="233">
@@ -23215,25 +23215,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F233" t="n">
-        <v>3.58050010044361</v>
+        <v>3.56668165949951</v>
       </c>
       <c r="G233" t="n">
-        <v>2.03213743368601</v>
+        <v>2.03614159226008</v>
       </c>
       <c r="H233" t="n">
-        <v>0.231710019946086</v>
+        <v>0.23293354751768</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0.0739575986504049</v>
+        <v>0.0741687847020298</v>
       </c>
       <c r="K233" t="n">
-        <v>-6.68097652559757</v>
+        <v>-6.67550858836349</v>
       </c>
       <c r="L233" t="n">
-        <v>-0.715826019352711</v>
+        <v>-0.715723431546298</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -23245,31 +23245,31 @@
         <v>0</v>
       </c>
       <c r="P233" t="n">
-        <v>-0.0683212258677145</v>
+        <v>-0.0683113510382995</v>
       </c>
       <c r="Q233" t="n">
-        <v>-0.0482322018492991</v>
+        <v>-0.0482252287581455</v>
       </c>
       <c r="R233" t="n">
-        <v>0.000202945296596091</v>
+        <v>0.000202915937497206</v>
       </c>
       <c r="S233" t="n">
-        <v>-0.00101639657675773</v>
+        <v>-0.00101624954193285</v>
       </c>
       <c r="T233" t="n">
-        <v>-0.000246105493538782</v>
+        <v>-0.000246069890905711</v>
       </c>
       <c r="U233" t="n">
-        <v>-0.00173762181611431</v>
+        <v>-0.00173737044921679</v>
       </c>
       <c r="V233" t="n">
-        <v>-0.000240559697536508</v>
+        <v>-0.000240524897121749</v>
       </c>
       <c r="W233" t="n">
-        <v>-5.91436861463351</v>
+        <v>-5.90457967475574</v>
       </c>
       <c r="X233" t="n">
-        <v>-0.997986039803619</v>
+        <v>-0.976382734990404</v>
       </c>
       <c r="Y233" t="e">
         <v>#NUM!</v>
@@ -23278,19 +23278,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA233" t="n">
-        <v>5.82151809025094</v>
+        <v>5.81318513992698</v>
       </c>
       <c r="AB233" t="n">
-        <v>-15.1001656021526</v>
+        <v>-15.0590577687034</v>
       </c>
       <c r="AC233" t="n">
-        <v>-8.35404029139007</v>
+        <v>-8.32460489343647</v>
       </c>
       <c r="AD233" t="n">
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>-5.42295707256856</v>
+        <v>-5.42078280420091</v>
       </c>
     </row>
     <row r="234">
@@ -23310,19 +23310,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F234" t="n">
-        <v>3.6008832698024</v>
+        <v>3.58681915901999</v>
       </c>
       <c r="G234" t="n">
-        <v>2.01324124556049</v>
+        <v>2.01722161843208</v>
       </c>
       <c r="H234" t="n">
-        <v>0.234408086220064</v>
+        <v>0.235645842474953</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0.0728010830921995</v>
+        <v>0.0709257755024889</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -23340,25 +23340,25 @@
         <v>0</v>
       </c>
       <c r="P234" t="n">
-        <v>-0.0406518917355554</v>
+        <v>-0.0406460139689392</v>
       </c>
       <c r="Q234" t="n">
-        <v>-0.0421545338553969</v>
+        <v>-0.0421484389450094</v>
       </c>
       <c r="R234" t="n">
-        <v>0.000199257723950149</v>
+        <v>0.000199228898315755</v>
       </c>
       <c r="S234" t="n">
-        <v>-0.00102118168850391</v>
+        <v>-0.00102103396141952</v>
       </c>
       <c r="T234" t="n">
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>-0.00170576872623044</v>
+        <v>-0.00170552196709636</v>
       </c>
       <c r="V234" t="n">
-        <v>-0.0000808476400810527</v>
+        <v>-0.0000808359442125396</v>
       </c>
       <c r="W234" t="n">
         <v>0</v>
@@ -23373,19 +23373,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA234" t="n">
-        <v>5.82481725337155</v>
+        <v>5.81427465283398</v>
       </c>
       <c r="AB234" t="n">
-        <v>-0.0854355399239037</v>
+        <v>-0.0854231942287362</v>
       </c>
       <c r="AC234" t="n">
-        <v>5.74474043125708</v>
+        <v>5.73420230224806</v>
       </c>
       <c r="AD234" t="n">
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -23405,19 +23405,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F235" t="n">
-        <v>3.55419131342856</v>
+        <v>3.54032774934682</v>
       </c>
       <c r="G235" t="n">
-        <v>1.99218795199887</v>
+        <v>1.99613451261478</v>
       </c>
       <c r="H235" t="n">
-        <v>0.236891268974758</v>
+        <v>0.238142117271145</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0.0713593967211659</v>
+        <v>0.0695212131680469</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -23435,25 +23435,25 @@
         <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>-0.0224127298025257</v>
+        <v>-0.022409488423022</v>
       </c>
       <c r="Q235" t="n">
-        <v>-0.0393082942887716</v>
+        <v>-0.0393026106929763</v>
       </c>
       <c r="R235" t="n">
-        <v>0.000195347197630985</v>
+        <v>0.000195318937695864</v>
       </c>
       <c r="S235" t="n">
-        <v>-0.00060243192778068</v>
+        <v>-0.000602344777792483</v>
       </c>
       <c r="T235" t="n">
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>-0.00134017561449183</v>
+        <v>-0.00133998174179264</v>
       </c>
       <c r="V235" t="n">
-        <v>-0.0000792523907588815</v>
+        <v>-0.0000792409257346894</v>
       </c>
       <c r="W235" t="n">
         <v>0</v>
@@ -23468,19 +23468,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA235" t="n">
-        <v>5.76000594526847</v>
+        <v>5.74967330662791</v>
       </c>
       <c r="AB235" t="n">
-        <v>-0.0635581412121001</v>
+        <v>-0.0635489542445201</v>
       </c>
       <c r="AC235" t="n">
-        <v>5.70039358694634</v>
+        <v>5.6900644019821</v>
       </c>
       <c r="AD235" t="n">
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -23500,19 +23500,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F236" t="n">
-        <v>3.51531773280946</v>
+        <v>3.50162432281797</v>
       </c>
       <c r="G236" t="n">
-        <v>1.97365007397347</v>
+        <v>1.97757310237238</v>
       </c>
       <c r="H236" t="n">
-        <v>0.239931441795108</v>
+        <v>0.241198322914313</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0.0701607737628257</v>
+        <v>0.0683534541565309</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -23530,16 +23530,16 @@
         <v>0</v>
       </c>
       <c r="P236" t="n">
-        <v>-0.0220131352469431</v>
+        <v>-0.0220099516396818</v>
       </c>
       <c r="Q236" t="n">
-        <v>-0.0384426166632188</v>
+        <v>-0.0384370581687646</v>
       </c>
       <c r="R236" t="n">
-        <v>0.000191882220196571</v>
+        <v>0.000191854461554047</v>
       </c>
       <c r="S236" t="n">
-        <v>-0.000600930741209028</v>
+        <v>-0.000600843808395421</v>
       </c>
       <c r="T236" t="n">
         <v>0</v>
@@ -23548,7 +23548,7 @@
         <v>0</v>
       </c>
       <c r="V236" t="n">
-        <v>-0.000077840488093452</v>
+        <v>-0.0000778292273450053</v>
       </c>
       <c r="W236" t="n">
         <v>0</v>
@@ -23563,19 +23563,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA236" t="n">
-        <v>5.70619759532021</v>
+        <v>5.69605173974185</v>
       </c>
       <c r="AB236" t="n">
-        <v>-0.0609519654886842</v>
+        <v>-0.0609431549178629</v>
       </c>
       <c r="AC236" t="n">
-        <v>5.64898837085382</v>
+        <v>5.63884594802628</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -23595,19 +23595,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F237" t="n">
-        <v>3.47321054898445</v>
+        <v>3.45970009396323</v>
       </c>
       <c r="G237" t="n">
-        <v>1.95442521053282</v>
+        <v>1.95831726703746</v>
       </c>
       <c r="H237" t="n">
-        <v>0.234050321110559</v>
+        <v>0.235286192361523</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>0.0688119296558737</v>
+        <v>0.0670393434064398</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -23625,16 +23625,16 @@
         <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>-0.0173112197637809</v>
+        <v>-0.017308716007735</v>
       </c>
       <c r="Q237" t="n">
-        <v>-0.0388104514204572</v>
+        <v>-0.0388048397659351</v>
       </c>
       <c r="R237" t="n">
-        <v>0.000443042923254768</v>
+        <v>0.000442978830190755</v>
       </c>
       <c r="S237" t="n">
-        <v>-0.000601138240837524</v>
+        <v>-0.00060105127805182</v>
       </c>
       <c r="T237" t="n">
         <v>0</v>
@@ -23643,7 +23643,7 @@
         <v>0</v>
       </c>
       <c r="V237" t="n">
-        <v>-0.0000763660228065846</v>
+        <v>-0.0000763549753931526</v>
       </c>
       <c r="W237" t="n">
         <v>0</v>
@@ -23658,19 +23658,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA237" t="n">
-        <v>5.6399194780742</v>
+        <v>5.62992460569785</v>
       </c>
       <c r="AB237" t="n">
-        <v>-0.056363421790418</v>
+        <v>-0.0563552739992262</v>
       </c>
       <c r="AC237" t="n">
-        <v>5.58697498436932</v>
+        <v>5.57698336812829</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -23696,13 +23696,13 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>0.228449919265009</v>
+        <v>0.229656260332657</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
       </c>
       <c r="J238" t="n">
-        <v>0.0676439575150105</v>
+        <v>0.0659014468804368</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -23723,13 +23723,13 @@
         <v>0</v>
       </c>
       <c r="Q238" t="n">
-        <v>-0.0306265926763216</v>
+        <v>-0.0306221638603038</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>-0.000502204815656503</v>
+        <v>-0.000502132164902111</v>
       </c>
       <c r="T238" t="n">
         <v>0</v>
@@ -23753,19 +23753,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA238" t="n">
-        <v>0.295929501370882</v>
+        <v>0.295396640072147</v>
       </c>
       <c r="AB238" t="n">
-        <v>-0.0311289610020127</v>
+        <v>-0.0311244595696384</v>
       </c>
       <c r="AC238" t="n">
-        <v>0.264898522262119</v>
+        <v>0.264370020668816</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -23791,13 +23791,13 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0.222824764294032</v>
+        <v>0.22400144166507</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0.0665022993056748</v>
+        <v>0.0647891873791906</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -23818,13 +23818,13 @@
         <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>-0.0292019463996334</v>
+        <v>-0.0291977235173183</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>-0.000396645839132258</v>
+        <v>-0.000396588458774972</v>
       </c>
       <c r="T239" t="n">
         <v>0</v>
@@ -23848,19 +23848,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA239" t="n">
-        <v>0.28916957894134</v>
+        <v>0.288636313966796</v>
       </c>
       <c r="AB239" t="n">
-        <v>-0.0295987152676964</v>
+        <v>-0.0295944350309416</v>
       </c>
       <c r="AC239" t="n">
-        <v>0.259661821673705</v>
+        <v>0.259132701410909</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -23886,13 +23886,13 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>0.217084172487286</v>
+        <v>0.218230573361025</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>0.0651185795937728</v>
+        <v>0.0634411009870588</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -23913,13 +23913,13 @@
         <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>-0.0286231606348469</v>
+        <v>-0.0286190214199126</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>-0.000293618955169596</v>
+        <v>-0.000293576479112495</v>
       </c>
       <c r="T240" t="n">
         <v>0</v>
@@ -23943,19 +23943,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.282052456079552</v>
+        <v>0.281524403247462</v>
       </c>
       <c r="AB240" t="n">
-        <v>-0.0289168688952376</v>
+        <v>-0.0289126872229968</v>
       </c>
       <c r="AC240" t="n">
-        <v>0.253222298008468</v>
+        <v>0.252698295218487</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -23981,13 +23981,13 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>0.211649403096106</v>
+        <v>0.212767139633834</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
       </c>
       <c r="J241" t="n">
-        <v>0.0639540474155803</v>
+        <v>0.0623065576410292</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -24008,13 +24008,13 @@
         <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>-0.0285306772592885</v>
+        <v>-0.0285265514128828</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>-0.000193758378148312</v>
+        <v>-0.000193730348217314</v>
       </c>
       <c r="T241" t="n">
         <v>0</v>
@@ -24038,19 +24038,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.27545959094879</v>
+        <v>0.274932733070201</v>
       </c>
       <c r="AB241" t="n">
-        <v>-0.0287244943582483</v>
+        <v>-0.0287203404942937</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.246819186118347</v>
+        <v>0.246296351048185</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -24103,13 +24103,13 @@
         <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>-0.00950251500132452</v>
+        <v>-0.00950114049277994</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>-0.0000967550409194685</v>
+        <v>-0.0000967410438978406</v>
       </c>
       <c r="T242" t="n">
         <v>0</v>
@@ -24136,16 +24136,16 @@
         <v>0</v>
       </c>
       <c r="AB242" t="n">
-        <v>-0.00959927979563127</v>
+        <v>-0.00959789129212495</v>
       </c>
       <c r="AC242" t="n">
-        <v>-0.00959927979563127</v>
+        <v>-0.00959789129212495</v>
       </c>
       <c r="AD242" t="n">
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>-0.00933488329082626</v>
+        <v>-0.00933353302638278</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -24231,16 +24231,16 @@
         <v>0</v>
       </c>
       <c r="AB243" t="n">
-        <v>-0.00933488329082626</v>
+        <v>-0.00933353302638278</v>
       </c>
       <c r="AC243" t="n">
-        <v>-0.00933488329082626</v>
+        <v>-0.00933353302638278</v>
       </c>
       <c r="AD243" t="n">
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -24293,7 +24293,7 @@
         <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>-0.00915105195514218</v>
+        <v>-0.00914972827811691</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -24326,16 +24326,16 @@
         <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>-0.00915105195514218</v>
+        <v>-0.00914972827811691</v>
       </c>
       <c r="AC244" t="n">
-        <v>-0.00915105195514218</v>
+        <v>-0.00914972827811691</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -24388,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="Q245" t="n">
-        <v>-0.00898367400999615</v>
+        <v>-0.00898237454070996</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -24421,16 +24421,16 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>-0.00898367400999615</v>
+        <v>-0.00898237454070996</v>
       </c>
       <c r="AC245" t="n">
-        <v>-0.00898367400999615</v>
+        <v>-0.00898237454070996</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -24525,7 +24525,7 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -24620,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>-0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
